--- a/preprocess/★★ 福壽家禽資料 ★★/筆記.xlsx
+++ b/preprocess/★★ 福壽家禽資料 ★★/筆記.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HoChePing\北科大_碩班_AI學程\期刊研究\使用LSTM模型預測福壽雞隻重量\Code程式碼\PersonalNote\DataSet_For_TransferLearning\★★ 福壽家禽資料 ★★\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4353151-38DD-46BB-90BE-93243C2718F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE95F9E-F4E9-4A0E-8183-FB08875933D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
-    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
+    <sheet name="DOE－實驗設計" sheetId="6" r:id="rId1"/>
+    <sheet name="DOE－拆解問題" sheetId="7" r:id="rId2"/>
+    <sheet name="分階段實驗" sheetId="8" r:id="rId3"/>
+    <sheet name="實驗步驟" sheetId="2" r:id="rId4"/>
+    <sheet name="正規化區分" sheetId="1" r:id="rId5"/>
+    <sheet name="Positive TL定義" sheetId="3" r:id="rId6"/>
+    <sheet name="Fwusow檔案說明" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="101">
   <si>
     <t>資料版本</t>
   </si>
@@ -92,18 +97,266 @@
   </si>
   <si>
     <t>Exp.5 Kaggle 0–21 → 福壽 0–31</t>
+  </si>
+  <si>
+    <t>判斷等級</t>
+  </si>
+  <si>
+    <t>條件</t>
+  </si>
+  <si>
+    <t>解讀</t>
+  </si>
+  <si>
+    <t>強正向遷移</t>
+  </si>
+  <si>
+    <t>MAE、RMSE 下降，R² 也明顯提升或轉正</t>
+  </si>
+  <si>
+    <t>可以主張 Positive Transfer Learning</t>
+  </si>
+  <si>
+    <t>部分正向遷移</t>
+  </si>
+  <si>
+    <t>MAE、RMSE 下降，但 R² 未轉正</t>
+  </si>
+  <si>
+    <t>可主張部分正向遷移</t>
+  </si>
+  <si>
+    <t>無正向遷移</t>
+  </si>
+  <si>
+    <t>MAE、RMSE、R² 都未優於 Without TL</t>
+  </si>
+  <si>
+    <t>說明後期外推困難或 domain gap</t>
+  </si>
+  <si>
+    <t>MAE、MSE、RMSE 皆下降，且 R² 明顯提升並轉正</t>
+  </si>
+  <si>
+    <t>可主張 Positive Transfer Learning 成立</t>
+  </si>
+  <si>
+    <t>MAE、MSE、RMSE 下降，R² 也比 Without TL 改善，但仍未轉正</t>
+  </si>
+  <si>
+    <t>可主張遷移學習有助於降低預測誤差，但尚未完整克服 Target 任務困難</t>
+  </si>
+  <si>
+    <t>無明顯正向遷移</t>
+  </si>
+  <si>
+    <t>MAE、RMSE 沒有明顯改善，或 R² 沒有優於 Without TL</t>
+  </si>
+  <si>
+    <t>不宜主張 Positive Transfer Learning</t>
+  </si>
+  <si>
+    <t>負向遷移</t>
+  </si>
+  <si>
+    <t>Transfer Learning 表現比 Without TL 更差</t>
+  </si>
+  <si>
+    <t>表示 Source 權重可能造成干擾或 domain gap 過大</t>
+  </si>
+  <si>
+    <t>檔案</t>
+  </si>
+  <si>
+    <t>是否適合畫福壽 0–21 mean curve</t>
+  </si>
+  <si>
+    <t>Fwusow_TargetData_daily_stats_0_21.csv</t>
+  </si>
+  <si>
+    <t>福壽 0–21 原始 daily statistics</t>
+  </si>
+  <si>
+    <t>最適合</t>
+  </si>
+  <si>
+    <t>Fwusow_TargetData_daily_stats_0_31.csv</t>
+  </si>
+  <si>
+    <t>福壽 0–31 原始 daily statistics</t>
+  </si>
+  <si>
+    <t>適合畫完整 0–31</t>
+  </si>
+  <si>
+    <t>Fwusow_TargetData_daily_stats_0_31_normalized_preview_reuse0_21.csv</t>
+  </si>
+  <si>
+    <t>使用 0–21 scaler 轉換後的 0–31 normalized preview</t>
+  </si>
+  <si>
+    <t>適合檢查 scaler 對齊，不建議當原始曲線第一張</t>
+  </si>
+  <si>
+    <t>Fwusow_TargetData_growth_curve_cleaned_0_31.csv</t>
+  </si>
+  <si>
+    <t>每條生長曲線的 long-format 原始整理資料</t>
+  </si>
+  <si>
+    <t>適合畫個體曲線</t>
+  </si>
+  <si>
+    <t>Fwusow_TargetData_growth_curve_matrix_0_31.xlsx</t>
+  </si>
+  <si>
+    <t>48 條曲線矩陣</t>
+  </si>
+  <si>
+    <t>適合看每條曲線分布</t>
+  </si>
+  <si>
+    <t>曲線</t>
+  </si>
+  <si>
+    <t>正規化方式</t>
+  </si>
+  <si>
+    <t>圖上意義</t>
+  </si>
+  <si>
+    <t>Kaggle 0–21</t>
+  </si>
+  <si>
+    <t>Kaggle 自己 0–21 normalize</t>
+  </si>
+  <si>
+    <t>Source 早期生長型態</t>
+  </si>
+  <si>
+    <t>FwuSow 0–21</t>
+  </si>
+  <si>
+    <t>FwuSow 0–21 normalize</t>
+  </si>
+  <si>
+    <t>Stage A Target 尺度</t>
+  </si>
+  <si>
+    <t>FwuSow 0–31</t>
+  </si>
+  <si>
+    <t>reuse FwuSow 0–21 scale</t>
+  </si>
+  <si>
+    <t>Stage B 外推區間</t>
+  </si>
+  <si>
+    <t>實驗編號</t>
+  </si>
+  <si>
+    <t>設定</t>
+  </si>
+  <si>
+    <t>Exp. A</t>
+  </si>
+  <si>
+    <t>福壽 0–35 Without TL</t>
+  </si>
+  <si>
+    <t>最重要 baseline</t>
+  </si>
+  <si>
+    <t>Exp. B</t>
+  </si>
+  <si>
+    <t>Kaggle 0–21 → 福壽 0–35</t>
+  </si>
+  <si>
+    <t>直接遷移 baseline</t>
+  </si>
+  <si>
+    <t>Exp. C</t>
+  </si>
+  <si>
+    <t>Kaggle 0–21 → 福壽 0–21 → 福壽 0–35</t>
+  </si>
+  <si>
+    <t>你的分階段策略</t>
+  </si>
+  <si>
+    <t>Exp. D</t>
+  </si>
+  <si>
+    <t>福壽 0–21 → 福壽 0–35，不使用 Kaggle</t>
+  </si>
+  <si>
+    <t>檢查 Kaggle Source 是否真的有幫助</t>
+  </si>
+  <si>
+    <t>問題</t>
+  </si>
+  <si>
+    <t>對應比較</t>
+  </si>
+  <si>
+    <t>TL 有沒有比 Without TL 好？</t>
+  </si>
+  <si>
+    <t>C vs A</t>
+  </si>
+  <si>
+    <t>分階段是否比直接遷移好？</t>
+  </si>
+  <si>
+    <t>C vs B</t>
+  </si>
+  <si>
+    <t>Kaggle Source 是否真的有幫助？</t>
+  </si>
+  <si>
+    <t>C vs D</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Stage A</t>
+  </si>
+  <si>
+    <t>Stage B</t>
+  </si>
+  <si>
+    <t>Kaggle 0–21 → FwuSow 0–21</t>
+  </si>
+  <si>
+    <t>Stage C</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -128,6 +381,15 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -146,23 +408,45 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 2" xfId="1" xr:uid="{54D98E0B-34C7-441B-BF8C-B1927612021C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -439,6 +723,309 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{187D14D0-F0E4-4D6E-9DA9-1C2E2EE1D818}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="33">
+      <c r="A4" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="33">
+      <c r="A5" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00A8C880-5EDF-4686-9ADA-5DBCF9E4FABD}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="36.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A6221C-1B55-4A19-ACAD-47485E596C43}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="3" width="35.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58CDCF19-3644-4173-80D4-40139E8EDA17}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="3" width="35.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="35.1" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
@@ -480,88 +1067,203 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58CDCF19-3644-4173-80D4-40139E8EDA17}">
-  <dimension ref="A1:C6"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B2FDBF-13D3-44EC-B21D-0096BBE6BB69}">
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="3" width="35.7109375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="31.5">
+      <c r="A2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="31.5">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="31.5">
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="31.5">
+      <c r="A11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="31.5">
+      <c r="A12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="31.5">
+      <c r="A13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABAAA1C-57F3-4E3C-8B50-0B87A2146085}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="3" width="45.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
     <row r="1" spans="1:3" ht="35.1" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="35.1" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>14</v>
+      <c r="A2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="35.1" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
+      <c r="A3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="35.1" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
+      <c r="A4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="35.1" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
+      <c r="A5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="35.1" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
+      <c r="A6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>